--- a/MY CLASSES/RE-ASSESSMENTS/COTATION SHEET_L 3 NETWORKING AND INTERNET TECHNOLOGY-IOT.xlsx
+++ b/MY CLASSES/RE-ASSESSMENTS/COTATION SHEET_L 3 NETWORKING AND INTERNET TECHNOLOGY-IOT.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Landry\3D Objects\ETEFOP Trainer Docs\Revised_COTATION SHEETS THIRD TERM 2024-2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Landry\3D Objects\ETEFOP Trainer Docs\ETEFOP-DOCS\MY CLASSES\RE-ASSESSMENTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$B$4:$O$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$B$4:$O$80</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="162">
   <si>
     <t>ACADEMIC YEAR 2024-2025</t>
   </si>
@@ -507,6 +507,12 @@
   </si>
   <si>
     <t>NITIS301</t>
+  </si>
+  <si>
+    <t>MUHIRE Germain</t>
+  </si>
+  <si>
+    <t>NTWARI KUNDA Aldo Serge</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1141,97 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="16">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FFFF00FF"/>
+          </stop>
+          <stop position="1">
+            <color auto="1"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor auto="1"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FFFF3399"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFF3399"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <gradientFill degree="90">
@@ -2182,7 +2278,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ176"/>
+  <dimension ref="A1:AJ178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="4" customWidth="1"/>
@@ -2202,8 +2298,8 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
-        <f>COUNTA(C19:C19966)+18</f>
-        <v>79</v>
+        <f>COUNTA(C19:C19968)+18</f>
+        <v>81</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -2362,7 +2458,7 @@
     <row r="12" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="J12" s="10" t="str">
-        <f>IFERROR(IF(OR(E12&gt;$E$18,F12&gt;$F$18,G12&gt;$G$18,H12&gt;$H$18,I12&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$108)&lt;=0,$D12=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E12:G12)*K$17/SUM(E$18:G$18))+(H12*K$17/H$18)+(I12*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E12:G12)*K$17/SUM(E$18:G$18))+(H12*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E12:G12)*K$17/SUM(E$18:G$18))+(I12*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H12*K$17/H$18)+(I12*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E12:G12)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H12*K$17/H$18,IF(I$18&gt;0,I12*K$17/I$18,"-")))))))))),"-")</f>
+        <f>IFERROR(IF(OR(E12&gt;$E$18,F12&gt;$F$18,G12&gt;$G$18,H12&gt;$H$18,I12&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D12=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E12:G12)*K$17/SUM(E$18:G$18))+(H12*K$17/H$18)+(I12*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E12:G12)*K$17/SUM(E$18:G$18))+(H12*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E12:G12)*K$17/SUM(E$18:G$18))+(I12*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H12*K$17/H$18)+(I12*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E12:G12)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H12*K$17/H$18,IF(I$18&gt;0,I12*K$17/I$18,"-")))))))))),"-")</f>
         <v/>
       </c>
       <c r="K12" s="11" t="str">
@@ -2565,7 +2661,9 @@
       <c r="K18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="25"/>
+      <c r="L18" s="25">
+        <v>20</v>
+      </c>
       <c r="M18" s="25"/>
       <c r="N18" s="25"/>
       <c r="O18" s="27" t="s">
@@ -2594,11 +2692,11 @@
       <c r="H19" s="31"/>
       <c r="I19" s="31"/>
       <c r="J19" s="32" t="str">
-        <f t="shared" ref="J19:J79" si="0">IFERROR(IF(OR(E19&gt;$E$18,F19&gt;$F$18,G19&gt;$G$18,H19&gt;$H$18,I19&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$108)&lt;=0,$D19=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E19:G19)*K$17/SUM(E$18:G$18))+(H19*K$17/H$18)+(I19*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E19:G19)*K$17/SUM(E$18:G$18))+(H19*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E19:G19)*K$17/SUM(E$18:G$18))+(I19*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H19*K$17/H$18)+(I19*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E19:G19)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H19*K$17/H$18,IF(I$18&gt;0,I19*K$17/I$18,"-")))))))))),"-")</f>
+        <f>IFERROR(IF(OR(E19&gt;$E$18,F19&gt;$F$18,G19&gt;$G$18,H19&gt;$H$18,I19&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D19=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E19:G19)*K$17/SUM(E$18:G$18))+(H19*K$17/H$18)+(I19*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E19:G19)*K$17/SUM(E$18:G$18))+(H19*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E19:G19)*K$17/SUM(E$18:G$18))+(I19*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H19*K$17/H$18)+(I19*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E19:G19)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H19*K$17/H$18,IF(I$18&gt;0,I19*K$17/I$18,"-")))))))))),"-")</f>
         <v/>
       </c>
       <c r="K19" s="33" t="str">
-        <f t="shared" ref="K19:K79" si="1">IF($O$15="","",IF(ISTEXT(J19),"",IF(J19&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
+        <f t="shared" ref="K19:K78" si="0">IF($O$15="","",IF(ISTEXT(J19),"",IF(J19&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
         <v/>
       </c>
       <c r="L19" s="34">
@@ -2607,7 +2705,7 @@
       <c r="M19" s="34"/>
       <c r="N19" s="34"/>
       <c r="O19" s="33" t="str">
-        <f t="shared" ref="O19:O79" si="2">IFERROR(IF(AND(ISNUMBER(J19),J19&gt;=$K$17*$P$15)," ",IF(AND(J19&gt;0,$O$16&lt;&gt;"Not yet Taught",$D19&lt;&gt;"",J19="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D19&lt;&gt;"",$L$18&gt;0,L19&gt;0,L19&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D19&lt;&gt;"",M19&gt;0,M19&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D19&lt;&gt;"",N19&gt;0,N19&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D19&lt;&gt;"",L19&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D19&lt;&gt;"",L19&lt;=0,M19&lt;=0,N19&lt;=0),"Re-Assessment",IF(AND(J19&gt;0,$D19&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
+        <f t="shared" ref="O19:O78" si="1">IFERROR(IF(AND(ISNUMBER(J19),J19&gt;=$K$17*$P$15)," ",IF(AND(J19&gt;0,$O$16&lt;&gt;"Not yet Taught",$D19&lt;&gt;"",J19="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D19&lt;&gt;"",$L$18&gt;0,L19&gt;0,L19&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D19&lt;&gt;"",M19&gt;0,M19&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D19&lt;&gt;"",N19&gt;0,N19&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D19&lt;&gt;"",L19&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D19&lt;&gt;"",L19&lt;=0,M19&lt;=0,N19&lt;=0),"Re-Assessment",IF(AND(J19&gt;0,$D19&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
         <v/>
       </c>
       <c r="P19" s="9"/>
@@ -2633,18 +2731,18 @@
       <c r="H20" s="34"/>
       <c r="I20" s="34"/>
       <c r="J20" s="32" t="str">
+        <f>IFERROR(IF(OR(E20&gt;$E$18,F20&gt;$F$18,G20&gt;$G$18,H20&gt;$H$18,I20&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D20=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E20:G20)*K$17/SUM(E$18:G$18))+(H20*K$17/H$18)+(I20*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E20:G20)*K$17/SUM(E$18:G$18))+(H20*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E20:G20)*K$17/SUM(E$18:G$18))+(I20*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H20*K$17/H$18)+(I20*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E20:G20)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H20*K$17/H$18,IF(I$18&gt;0,I20*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K20" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L20" s="34"/>
       <c r="M20" s="34"/>
       <c r="N20" s="34"/>
       <c r="O20" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P20" s="9"/>
@@ -2670,18 +2768,18 @@
       <c r="H21" s="34"/>
       <c r="I21" s="34"/>
       <c r="J21" s="32" t="str">
+        <f>IFERROR(IF(OR(E21&gt;$E$18,F21&gt;$F$18,G21&gt;$G$18,H21&gt;$H$18,I21&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D21=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E21:G21)*K$17/SUM(E$18:G$18))+(H21*K$17/H$18)+(I21*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E21:G21)*K$17/SUM(E$18:G$18))+(H21*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E21:G21)*K$17/SUM(E$18:G$18))+(I21*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H21*K$17/H$18)+(I21*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E21:G21)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H21*K$17/H$18,IF(I$18&gt;0,I21*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K21" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K21" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
       <c r="N21" s="34"/>
       <c r="O21" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P21" s="9"/>
@@ -2707,18 +2805,18 @@
       <c r="H22" s="34"/>
       <c r="I22" s="34"/>
       <c r="J22" s="32" t="str">
+        <f>IFERROR(IF(OR(E22&gt;$E$18,F22&gt;$F$18,G22&gt;$G$18,H22&gt;$H$18,I22&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D22=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E22:G22)*K$17/SUM(E$18:G$18))+(H22*K$17/H$18)+(I22*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E22:G22)*K$17/SUM(E$18:G$18))+(H22*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E22:G22)*K$17/SUM(E$18:G$18))+(I22*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H22*K$17/H$18)+(I22*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E22:G22)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H22*K$17/H$18,IF(I$18&gt;0,I22*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K22" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K22" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
       <c r="N22" s="34"/>
       <c r="O22" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P22" s="9"/>
@@ -2744,18 +2842,18 @@
       <c r="H23" s="31"/>
       <c r="I23" s="31"/>
       <c r="J23" s="32" t="str">
+        <f>IFERROR(IF(OR(E23&gt;$E$18,F23&gt;$F$18,G23&gt;$G$18,H23&gt;$H$18,I23&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D23=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E23:G23)*K$17/SUM(E$18:G$18))+(H23*K$17/H$18)+(I23*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E23:G23)*K$17/SUM(E$18:G$18))+(H23*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E23:G23)*K$17/SUM(E$18:G$18))+(I23*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H23*K$17/H$18)+(I23*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E23:G23)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H23*K$17/H$18,IF(I$18&gt;0,I23*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K23" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
       <c r="N23" s="34"/>
       <c r="O23" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P23" s="9"/>
@@ -2781,18 +2879,18 @@
       <c r="H24" s="34"/>
       <c r="I24" s="34"/>
       <c r="J24" s="32" t="str">
+        <f>IFERROR(IF(OR(E24&gt;$E$18,F24&gt;$F$18,G24&gt;$G$18,H24&gt;$H$18,I24&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D24=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E24:G24)*K$17/SUM(E$18:G$18))+(H24*K$17/H$18)+(I24*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E24:G24)*K$17/SUM(E$18:G$18))+(H24*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E24:G24)*K$17/SUM(E$18:G$18))+(I24*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H24*K$17/H$18)+(I24*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E24:G24)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H24*K$17/H$18,IF(I$18&gt;0,I24*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K24" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
       <c r="N24" s="34"/>
       <c r="O24" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P24" s="9"/>
@@ -2818,18 +2916,18 @@
       <c r="H25" s="37"/>
       <c r="I25" s="37"/>
       <c r="J25" s="32" t="str">
+        <f>IFERROR(IF(OR(E25&gt;$E$18,F25&gt;$F$18,G25&gt;$G$18,H25&gt;$H$18,I25&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D25=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E25:G25)*K$17/SUM(E$18:G$18))+(H25*K$17/H$18)+(I25*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E25:G25)*K$17/SUM(E$18:G$18))+(H25*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E25:G25)*K$17/SUM(E$18:G$18))+(I25*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H25*K$17/H$18)+(I25*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E25:G25)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H25*K$17/H$18,IF(I$18&gt;0,I25*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K25" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L25" s="34"/>
       <c r="M25" s="34"/>
       <c r="N25" s="34"/>
       <c r="O25" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P25" s="9"/>
@@ -2855,18 +2953,18 @@
       <c r="H26" s="34"/>
       <c r="I26" s="34"/>
       <c r="J26" s="32" t="str">
+        <f>IFERROR(IF(OR(E26&gt;$E$18,F26&gt;$F$18,G26&gt;$G$18,H26&gt;$H$18,I26&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D26=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E26:G26)*K$17/SUM(E$18:G$18))+(H26*K$17/H$18)+(I26*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E26:G26)*K$17/SUM(E$18:G$18))+(H26*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E26:G26)*K$17/SUM(E$18:G$18))+(I26*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H26*K$17/H$18)+(I26*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E26:G26)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H26*K$17/H$18,IF(I$18&gt;0,I26*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K26" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K26" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L26" s="34"/>
       <c r="M26" s="34"/>
       <c r="N26" s="34"/>
       <c r="O26" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P26" s="9"/>
@@ -2892,18 +2990,18 @@
       <c r="H27" s="34"/>
       <c r="I27" s="34"/>
       <c r="J27" s="32" t="str">
+        <f>IFERROR(IF(OR(E27&gt;$E$18,F27&gt;$F$18,G27&gt;$G$18,H27&gt;$H$18,I27&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D27=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E27:G27)*K$17/SUM(E$18:G$18))+(H27*K$17/H$18)+(I27*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E27:G27)*K$17/SUM(E$18:G$18))+(H27*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E27:G27)*K$17/SUM(E$18:G$18))+(I27*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H27*K$17/H$18)+(I27*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E27:G27)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H27*K$17/H$18,IF(I$18&gt;0,I27*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K27" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K27" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
       <c r="N27" s="34"/>
       <c r="O27" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P27" s="9"/>
@@ -2929,11 +3027,11 @@
       <c r="H28" s="34"/>
       <c r="I28" s="34"/>
       <c r="J28" s="32" t="str">
+        <f>IFERROR(IF(OR(E28&gt;$E$18,F28&gt;$F$18,G28&gt;$G$18,H28&gt;$H$18,I28&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D28=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E28:G28)*K$17/SUM(E$18:G$18))+(H28*K$17/H$18)+(I28*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E28:G28)*K$17/SUM(E$18:G$18))+(H28*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E28:G28)*K$17/SUM(E$18:G$18))+(I28*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H28*K$17/H$18)+(I28*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E28:G28)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H28*K$17/H$18,IF(I$18&gt;0,I28*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K28" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L28" s="34">
@@ -2942,7 +3040,7 @@
       <c r="M28" s="34"/>
       <c r="N28" s="34"/>
       <c r="O28" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P28" s="9"/>
@@ -2968,11 +3066,11 @@
       <c r="H29" s="37"/>
       <c r="I29" s="37"/>
       <c r="J29" s="32" t="str">
+        <f>IFERROR(IF(OR(E29&gt;$E$18,F29&gt;$F$18,G29&gt;$G$18,H29&gt;$H$18,I29&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D29=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E29:G29)*K$17/SUM(E$18:G$18))+(H29*K$17/H$18)+(I29*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E29:G29)*K$17/SUM(E$18:G$18))+(H29*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E29:G29)*K$17/SUM(E$18:G$18))+(I29*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H29*K$17/H$18)+(I29*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E29:G29)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H29*K$17/H$18,IF(I$18&gt;0,I29*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K29" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L29" s="34">
@@ -2981,7 +3079,7 @@
       <c r="M29" s="34"/>
       <c r="N29" s="34"/>
       <c r="O29" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P29" s="9"/>
@@ -3007,11 +3105,11 @@
       <c r="H30" s="34"/>
       <c r="I30" s="34"/>
       <c r="J30" s="32" t="str">
+        <f>IFERROR(IF(OR(E30&gt;$E$18,F30&gt;$F$18,G30&gt;$G$18,H30&gt;$H$18,I30&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D30=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E30:G30)*K$17/SUM(E$18:G$18))+(H30*K$17/H$18)+(I30*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E30:G30)*K$17/SUM(E$18:G$18))+(H30*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E30:G30)*K$17/SUM(E$18:G$18))+(I30*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H30*K$17/H$18)+(I30*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E30:G30)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H30*K$17/H$18,IF(I$18&gt;0,I30*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K30" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K30" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L30" s="34">
@@ -3020,7 +3118,7 @@
       <c r="M30" s="34"/>
       <c r="N30" s="34"/>
       <c r="O30" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P30" s="9"/>
@@ -3046,18 +3144,18 @@
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="J31" s="32" t="str">
+        <f>IFERROR(IF(OR(E31&gt;$E$18,F31&gt;$F$18,G31&gt;$G$18,H31&gt;$H$18,I31&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D31=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E31:G31)*K$17/SUM(E$18:G$18))+(H31*K$17/H$18)+(I31*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E31:G31)*K$17/SUM(E$18:G$18))+(H31*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E31:G31)*K$17/SUM(E$18:G$18))+(I31*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H31*K$17/H$18)+(I31*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E31:G31)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H31*K$17/H$18,IF(I$18&gt;0,I31*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K31" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K31" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L31" s="34"/>
       <c r="M31" s="34"/>
       <c r="N31" s="34"/>
       <c r="O31" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P31" s="9"/>
@@ -3083,18 +3181,18 @@
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="J32" s="32" t="str">
+        <f>IFERROR(IF(OR(E32&gt;$E$18,F32&gt;$F$18,G32&gt;$G$18,H32&gt;$H$18,I32&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D32=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E32:G32)*K$17/SUM(E$18:G$18))+(H32*K$17/H$18)+(I32*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E32:G32)*K$17/SUM(E$18:G$18))+(H32*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E32:G32)*K$17/SUM(E$18:G$18))+(I32*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H32*K$17/H$18)+(I32*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E32:G32)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H32*K$17/H$18,IF(I$18&gt;0,I32*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K32" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K32" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L32" s="34"/>
       <c r="M32" s="34"/>
       <c r="N32" s="34"/>
       <c r="O32" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P32" s="9"/>
@@ -3120,11 +3218,11 @@
       <c r="H33" s="34"/>
       <c r="I33" s="34"/>
       <c r="J33" s="32" t="str">
+        <f>IFERROR(IF(OR(E33&gt;$E$18,F33&gt;$F$18,G33&gt;$G$18,H33&gt;$H$18,I33&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D33=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E33:G33)*K$17/SUM(E$18:G$18))+(H33*K$17/H$18)+(I33*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E33:G33)*K$17/SUM(E$18:G$18))+(H33*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E33:G33)*K$17/SUM(E$18:G$18))+(I33*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H33*K$17/H$18)+(I33*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E33:G33)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H33*K$17/H$18,IF(I$18&gt;0,I33*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K33" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L33" s="34">
@@ -3133,7 +3231,7 @@
       <c r="M33" s="34"/>
       <c r="N33" s="34"/>
       <c r="O33" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P33" s="9"/>
@@ -3159,18 +3257,18 @@
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="J34" s="32" t="str">
+        <f>IFERROR(IF(OR(E34&gt;$E$18,F34&gt;$F$18,G34&gt;$G$18,H34&gt;$H$18,I34&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D34=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E34:G34)*K$17/SUM(E$18:G$18))+(H34*K$17/H$18)+(I34*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E34:G34)*K$17/SUM(E$18:G$18))+(H34*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E34:G34)*K$17/SUM(E$18:G$18))+(I34*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H34*K$17/H$18)+(I34*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E34:G34)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H34*K$17/H$18,IF(I$18&gt;0,I34*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K34" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K34" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L34" s="34"/>
       <c r="M34" s="34"/>
       <c r="N34" s="34"/>
       <c r="O34" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P34" s="9"/>
@@ -3196,11 +3294,11 @@
       <c r="H35" s="34"/>
       <c r="I35" s="34"/>
       <c r="J35" s="32" t="str">
+        <f>IFERROR(IF(OR(E35&gt;$E$18,F35&gt;$F$18,G35&gt;$G$18,H35&gt;$H$18,I35&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D35=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E35:G35)*K$17/SUM(E$18:G$18))+(H35*K$17/H$18)+(I35*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E35:G35)*K$17/SUM(E$18:G$18))+(H35*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E35:G35)*K$17/SUM(E$18:G$18))+(I35*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H35*K$17/H$18)+(I35*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E35:G35)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H35*K$17/H$18,IF(I$18&gt;0,I35*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K35" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K35" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L35" s="34">
@@ -3209,7 +3307,7 @@
       <c r="M35" s="34"/>
       <c r="N35" s="34"/>
       <c r="O35" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P35" s="9"/>
@@ -3235,18 +3333,18 @@
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="J36" s="32" t="str">
+        <f>IFERROR(IF(OR(E36&gt;$E$18,F36&gt;$F$18,G36&gt;$G$18,H36&gt;$H$18,I36&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D36=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E36:G36)*K$17/SUM(E$18:G$18))+(H36*K$17/H$18)+(I36*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E36:G36)*K$17/SUM(E$18:G$18))+(H36*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E36:G36)*K$17/SUM(E$18:G$18))+(I36*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H36*K$17/H$18)+(I36*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E36:G36)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H36*K$17/H$18,IF(I$18&gt;0,I36*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K36" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K36" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L36" s="34"/>
       <c r="M36" s="34"/>
       <c r="N36" s="34"/>
       <c r="O36" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P36" s="9"/>
@@ -3272,18 +3370,18 @@
       <c r="H37" s="34"/>
       <c r="I37" s="34"/>
       <c r="J37" s="32" t="str">
+        <f>IFERROR(IF(OR(E37&gt;$E$18,F37&gt;$F$18,G37&gt;$G$18,H37&gt;$H$18,I37&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D37=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E37:G37)*K$17/SUM(E$18:G$18))+(H37*K$17/H$18)+(I37*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E37:G37)*K$17/SUM(E$18:G$18))+(H37*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E37:G37)*K$17/SUM(E$18:G$18))+(I37*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H37*K$17/H$18)+(I37*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E37:G37)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H37*K$17/H$18,IF(I$18&gt;0,I37*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K37" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K37" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L37" s="34"/>
       <c r="M37" s="34"/>
       <c r="N37" s="34"/>
       <c r="O37" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P37" s="9"/>
@@ -3309,18 +3407,18 @@
       <c r="H38" s="34"/>
       <c r="I38" s="34"/>
       <c r="J38" s="32" t="str">
+        <f>IFERROR(IF(OR(E38&gt;$E$18,F38&gt;$F$18,G38&gt;$G$18,H38&gt;$H$18,I38&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D38=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E38:G38)*K$17/SUM(E$18:G$18))+(H38*K$17/H$18)+(I38*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E38:G38)*K$17/SUM(E$18:G$18))+(H38*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E38:G38)*K$17/SUM(E$18:G$18))+(I38*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H38*K$17/H$18)+(I38*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E38:G38)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H38*K$17/H$18,IF(I$18&gt;0,I38*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K38" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K38" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L38" s="34"/>
       <c r="M38" s="34"/>
       <c r="N38" s="34"/>
       <c r="O38" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P38" s="9"/>
@@ -3346,18 +3444,18 @@
       <c r="H39" s="31"/>
       <c r="I39" s="31"/>
       <c r="J39" s="32" t="str">
+        <f>IFERROR(IF(OR(E39&gt;$E$18,F39&gt;$F$18,G39&gt;$G$18,H39&gt;$H$18,I39&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D39=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E39:G39)*K$17/SUM(E$18:G$18))+(H39*K$17/H$18)+(I39*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E39:G39)*K$17/SUM(E$18:G$18))+(H39*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E39:G39)*K$17/SUM(E$18:G$18))+(I39*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H39*K$17/H$18)+(I39*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E39:G39)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H39*K$17/H$18,IF(I$18&gt;0,I39*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K39" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K39" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L39" s="34"/>
       <c r="M39" s="34"/>
       <c r="N39" s="34"/>
       <c r="O39" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P39" s="9"/>
@@ -3383,11 +3481,11 @@
       <c r="H40" s="34"/>
       <c r="I40" s="34"/>
       <c r="J40" s="32" t="str">
+        <f>IFERROR(IF(OR(E40&gt;$E$18,F40&gt;$F$18,G40&gt;$G$18,H40&gt;$H$18,I40&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D40=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E40:G40)*K$17/SUM(E$18:G$18))+(H40*K$17/H$18)+(I40*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E40:G40)*K$17/SUM(E$18:G$18))+(H40*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E40:G40)*K$17/SUM(E$18:G$18))+(I40*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H40*K$17/H$18)+(I40*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E40:G40)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H40*K$17/H$18,IF(I$18&gt;0,I40*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K40" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K40" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L40" s="34">
@@ -3396,7 +3494,7 @@
       <c r="M40" s="34"/>
       <c r="N40" s="34"/>
       <c r="O40" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P40" s="9"/>
@@ -3422,18 +3520,18 @@
       <c r="H41" s="37"/>
       <c r="I41" s="37"/>
       <c r="J41" s="32" t="str">
+        <f>IFERROR(IF(OR(E41&gt;$E$18,F41&gt;$F$18,G41&gt;$G$18,H41&gt;$H$18,I41&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D41=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E41:G41)*K$17/SUM(E$18:G$18))+(H41*K$17/H$18)+(I41*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E41:G41)*K$17/SUM(E$18:G$18))+(H41*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E41:G41)*K$17/SUM(E$18:G$18))+(I41*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H41*K$17/H$18)+(I41*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E41:G41)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H41*K$17/H$18,IF(I$18&gt;0,I41*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K41" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K41" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L41" s="34"/>
       <c r="M41" s="34"/>
       <c r="N41" s="34"/>
       <c r="O41" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P41" s="9"/>
@@ -3459,18 +3557,18 @@
       <c r="H42" s="37"/>
       <c r="I42" s="37"/>
       <c r="J42" s="32" t="str">
+        <f>IFERROR(IF(OR(E42&gt;$E$18,F42&gt;$F$18,G42&gt;$G$18,H42&gt;$H$18,I42&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D42=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E42:G42)*K$17/SUM(E$18:G$18))+(H42*K$17/H$18)+(I42*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E42:G42)*K$17/SUM(E$18:G$18))+(H42*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E42:G42)*K$17/SUM(E$18:G$18))+(I42*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H42*K$17/H$18)+(I42*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E42:G42)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H42*K$17/H$18,IF(I$18&gt;0,I42*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K42" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K42" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L42" s="34"/>
       <c r="M42" s="34"/>
       <c r="N42" s="34"/>
       <c r="O42" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P42" s="9"/>
@@ -3496,18 +3594,18 @@
       <c r="H43" s="34"/>
       <c r="I43" s="34"/>
       <c r="J43" s="32" t="str">
+        <f>IFERROR(IF(OR(E43&gt;$E$18,F43&gt;$F$18,G43&gt;$G$18,H43&gt;$H$18,I43&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D43=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E43:G43)*K$17/SUM(E$18:G$18))+(H43*K$17/H$18)+(I43*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E43:G43)*K$17/SUM(E$18:G$18))+(H43*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E43:G43)*K$17/SUM(E$18:G$18))+(I43*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H43*K$17/H$18)+(I43*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E43:G43)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H43*K$17/H$18,IF(I$18&gt;0,I43*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K43" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K43" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L43" s="34"/>
       <c r="M43" s="34"/>
       <c r="N43" s="34"/>
       <c r="O43" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P43" s="9"/>
@@ -3533,18 +3631,18 @@
       <c r="H44" s="31"/>
       <c r="I44" s="31"/>
       <c r="J44" s="32" t="str">
+        <f>IFERROR(IF(OR(E44&gt;$E$18,F44&gt;$F$18,G44&gt;$G$18,H44&gt;$H$18,I44&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D44=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E44:G44)*K$17/SUM(E$18:G$18))+(H44*K$17/H$18)+(I44*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E44:G44)*K$17/SUM(E$18:G$18))+(H44*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E44:G44)*K$17/SUM(E$18:G$18))+(I44*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H44*K$17/H$18)+(I44*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E44:G44)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H44*K$17/H$18,IF(I$18&gt;0,I44*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K44" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K44" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L44" s="34"/>
       <c r="M44" s="34"/>
       <c r="N44" s="34"/>
       <c r="O44" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P44" s="9"/>
@@ -3570,11 +3668,11 @@
       <c r="H45" s="37"/>
       <c r="I45" s="37"/>
       <c r="J45" s="32" t="str">
+        <f>IFERROR(IF(OR(E45&gt;$E$18,F45&gt;$F$18,G45&gt;$G$18,H45&gt;$H$18,I45&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D45=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E45:G45)*K$17/SUM(E$18:G$18))+(H45*K$17/H$18)+(I45*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E45:G45)*K$17/SUM(E$18:G$18))+(H45*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E45:G45)*K$17/SUM(E$18:G$18))+(I45*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H45*K$17/H$18)+(I45*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E45:G45)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H45*K$17/H$18,IF(I$18&gt;0,I45*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K45" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K45" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L45" s="34">
@@ -3583,7 +3681,7 @@
       <c r="M45" s="34"/>
       <c r="N45" s="34"/>
       <c r="O45" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P45" s="9"/>
@@ -3609,18 +3707,18 @@
       <c r="H46" s="34"/>
       <c r="I46" s="34"/>
       <c r="J46" s="32" t="str">
+        <f>IFERROR(IF(OR(E46&gt;$E$18,F46&gt;$F$18,G46&gt;$G$18,H46&gt;$H$18,I46&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D46=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E46:G46)*K$17/SUM(E$18:G$18))+(H46*K$17/H$18)+(I46*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E46:G46)*K$17/SUM(E$18:G$18))+(H46*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E46:G46)*K$17/SUM(E$18:G$18))+(I46*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H46*K$17/H$18)+(I46*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E46:G46)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H46*K$17/H$18,IF(I$18&gt;0,I46*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K46" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K46" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L46" s="34"/>
       <c r="M46" s="34"/>
       <c r="N46" s="34"/>
       <c r="O46" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P46" s="9"/>
@@ -3646,18 +3744,18 @@
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
       <c r="J47" s="32" t="str">
+        <f>IFERROR(IF(OR(E47&gt;$E$18,F47&gt;$F$18,G47&gt;$G$18,H47&gt;$H$18,I47&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D47=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E47:G47)*K$17/SUM(E$18:G$18))+(H47*K$17/H$18)+(I47*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E47:G47)*K$17/SUM(E$18:G$18))+(H47*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E47:G47)*K$17/SUM(E$18:G$18))+(I47*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H47*K$17/H$18)+(I47*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E47:G47)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H47*K$17/H$18,IF(I$18&gt;0,I47*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K47" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K47" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L47" s="34"/>
       <c r="M47" s="34"/>
       <c r="N47" s="34"/>
       <c r="O47" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P47" s="9"/>
@@ -3683,18 +3781,18 @@
       <c r="H48" s="39"/>
       <c r="I48" s="39"/>
       <c r="J48" s="10" t="str">
+        <f>IFERROR(IF(OR(E48&gt;$E$18,F48&gt;$F$18,G48&gt;$G$18,H48&gt;$H$18,I48&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D48=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E48:G48)*K$17/SUM(E$18:G$18))+(H48*K$17/H$18)+(I48*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E48:G48)*K$17/SUM(E$18:G$18))+(H48*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E48:G48)*K$17/SUM(E$18:G$18))+(I48*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H48*K$17/H$18)+(I48*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E48:G48)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H48*K$17/H$18,IF(I$18&gt;0,I48*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K48" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K48" s="11" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L48" s="39"/>
       <c r="M48" s="39"/>
       <c r="N48" s="39"/>
       <c r="O48" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P48" s="9"/>
@@ -3720,18 +3818,18 @@
       <c r="H49" s="34"/>
       <c r="I49" s="34"/>
       <c r="J49" s="32" t="str">
+        <f>IFERROR(IF(OR(E49&gt;$E$18,F49&gt;$F$18,G49&gt;$G$18,H49&gt;$H$18,I49&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D49=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E49:G49)*K$17/SUM(E$18:G$18))+(H49*K$17/H$18)+(I49*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E49:G49)*K$17/SUM(E$18:G$18))+(H49*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E49:G49)*K$17/SUM(E$18:G$18))+(I49*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H49*K$17/H$18)+(I49*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E49:G49)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H49*K$17/H$18,IF(I$18&gt;0,I49*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K49" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K49" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L49" s="34"/>
       <c r="M49" s="34"/>
       <c r="N49" s="34"/>
       <c r="O49" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P49" s="9"/>
@@ -3757,11 +3855,11 @@
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
       <c r="J50" s="32" t="str">
+        <f>IFERROR(IF(OR(E50&gt;$E$18,F50&gt;$F$18,G50&gt;$G$18,H50&gt;$H$18,I50&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D50=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E50:G50)*K$17/SUM(E$18:G$18))+(H50*K$17/H$18)+(I50*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E50:G50)*K$17/SUM(E$18:G$18))+(H50*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E50:G50)*K$17/SUM(E$18:G$18))+(I50*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H50*K$17/H$18)+(I50*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E50:G50)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H50*K$17/H$18,IF(I$18&gt;0,I50*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K50" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K50" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L50" s="34">
@@ -3770,7 +3868,7 @@
       <c r="M50" s="34"/>
       <c r="N50" s="34"/>
       <c r="O50" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P50" s="9"/>
@@ -3796,11 +3894,11 @@
       <c r="H51" s="34"/>
       <c r="I51" s="34"/>
       <c r="J51" s="32" t="str">
+        <f>IFERROR(IF(OR(E51&gt;$E$18,F51&gt;$F$18,G51&gt;$G$18,H51&gt;$H$18,I51&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D51=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E51:G51)*K$17/SUM(E$18:G$18))+(H51*K$17/H$18)+(I51*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E51:G51)*K$17/SUM(E$18:G$18))+(H51*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E51:G51)*K$17/SUM(E$18:G$18))+(I51*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H51*K$17/H$18)+(I51*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E51:G51)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H51*K$17/H$18,IF(I$18&gt;0,I51*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K51" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K51" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L51" s="34">
@@ -3809,7 +3907,7 @@
       <c r="M51" s="34"/>
       <c r="N51" s="34"/>
       <c r="O51" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P51" s="9"/>
@@ -3835,11 +3933,11 @@
       <c r="H52" s="31"/>
       <c r="I52" s="31"/>
       <c r="J52" s="32" t="str">
+        <f>IFERROR(IF(OR(E52&gt;$E$18,F52&gt;$F$18,G52&gt;$G$18,H52&gt;$H$18,I52&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D52=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E52:G52)*K$17/SUM(E$18:G$18))+(H52*K$17/H$18)+(I52*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E52:G52)*K$17/SUM(E$18:G$18))+(H52*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E52:G52)*K$17/SUM(E$18:G$18))+(I52*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H52*K$17/H$18)+(I52*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E52:G52)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H52*K$17/H$18,IF(I$18&gt;0,I52*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K52" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K52" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L52" s="34">
@@ -3848,7 +3946,7 @@
       <c r="M52" s="34"/>
       <c r="N52" s="34"/>
       <c r="O52" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P52" s="9"/>
@@ -3874,11 +3972,11 @@
       <c r="H53" s="37"/>
       <c r="I53" s="37"/>
       <c r="J53" s="32" t="str">
+        <f>IFERROR(IF(OR(E53&gt;$E$18,F53&gt;$F$18,G53&gt;$G$18,H53&gt;$H$18,I53&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D53=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E53:G53)*K$17/SUM(E$18:G$18))+(H53*K$17/H$18)+(I53*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E53:G53)*K$17/SUM(E$18:G$18))+(H53*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E53:G53)*K$17/SUM(E$18:G$18))+(I53*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H53*K$17/H$18)+(I53*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E53:G53)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H53*K$17/H$18,IF(I$18&gt;0,I53*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K53" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K53" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L53" s="34">
@@ -3887,7 +3985,7 @@
       <c r="M53" s="34"/>
       <c r="N53" s="34"/>
       <c r="O53" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P53" s="9"/>
@@ -3913,18 +4011,18 @@
       <c r="H54" s="39"/>
       <c r="I54" s="39"/>
       <c r="J54" s="10" t="str">
+        <f>IFERROR(IF(OR(E54&gt;$E$18,F54&gt;$F$18,G54&gt;$G$18,H54&gt;$H$18,I54&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D54=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E54:G54)*K$17/SUM(E$18:G$18))+(H54*K$17/H$18)+(I54*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E54:G54)*K$17/SUM(E$18:G$18))+(H54*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E54:G54)*K$17/SUM(E$18:G$18))+(I54*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H54*K$17/H$18)+(I54*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E54:G54)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H54*K$17/H$18,IF(I$18&gt;0,I54*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K54" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K54" s="11" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L54" s="39"/>
       <c r="M54" s="39"/>
       <c r="N54" s="39"/>
       <c r="O54" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P54" s="9"/>
@@ -3950,18 +4048,18 @@
       <c r="H55" s="37"/>
       <c r="I55" s="37"/>
       <c r="J55" s="32" t="str">
+        <f>IFERROR(IF(OR(E55&gt;$E$18,F55&gt;$F$18,G55&gt;$G$18,H55&gt;$H$18,I55&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D55=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E55:G55)*K$17/SUM(E$18:G$18))+(H55*K$17/H$18)+(I55*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E55:G55)*K$17/SUM(E$18:G$18))+(H55*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E55:G55)*K$17/SUM(E$18:G$18))+(I55*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H55*K$17/H$18)+(I55*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E55:G55)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H55*K$17/H$18,IF(I$18&gt;0,I55*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K55" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K55" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L55" s="34"/>
       <c r="M55" s="34"/>
       <c r="N55" s="34"/>
       <c r="O55" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P55" s="9"/>
@@ -3987,18 +4085,18 @@
       <c r="H56" s="34"/>
       <c r="I56" s="34"/>
       <c r="J56" s="32" t="str">
+        <f>IFERROR(IF(OR(E56&gt;$E$18,F56&gt;$F$18,G56&gt;$G$18,H56&gt;$H$18,I56&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D56=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E56:G56)*K$17/SUM(E$18:G$18))+(H56*K$17/H$18)+(I56*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E56:G56)*K$17/SUM(E$18:G$18))+(H56*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E56:G56)*K$17/SUM(E$18:G$18))+(I56*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H56*K$17/H$18)+(I56*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E56:G56)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H56*K$17/H$18,IF(I$18&gt;0,I56*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K56" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K56" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L56" s="34"/>
       <c r="M56" s="34"/>
       <c r="N56" s="34"/>
       <c r="O56" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P56" s="9"/>
@@ -4024,18 +4122,18 @@
       <c r="H57" s="34"/>
       <c r="I57" s="34"/>
       <c r="J57" s="32" t="str">
+        <f>IFERROR(IF(OR(E57&gt;$E$18,F57&gt;$F$18,G57&gt;$G$18,H57&gt;$H$18,I57&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D57=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E57:G57)*K$17/SUM(E$18:G$18))+(H57*K$17/H$18)+(I57*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E57:G57)*K$17/SUM(E$18:G$18))+(H57*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E57:G57)*K$17/SUM(E$18:G$18))+(I57*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H57*K$17/H$18)+(I57*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E57:G57)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H57*K$17/H$18,IF(I$18&gt;0,I57*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K57" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K57" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L57" s="34"/>
       <c r="M57" s="34"/>
       <c r="N57" s="34"/>
       <c r="O57" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P57" s="9"/>
@@ -4061,18 +4159,18 @@
       <c r="H58" s="31"/>
       <c r="I58" s="31"/>
       <c r="J58" s="32" t="str">
+        <f>IFERROR(IF(OR(E58&gt;$E$18,F58&gt;$F$18,G58&gt;$G$18,H58&gt;$H$18,I58&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D58=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E58:G58)*K$17/SUM(E$18:G$18))+(H58*K$17/H$18)+(I58*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E58:G58)*K$17/SUM(E$18:G$18))+(H58*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E58:G58)*K$17/SUM(E$18:G$18))+(I58*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H58*K$17/H$18)+(I58*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E58:G58)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H58*K$17/H$18,IF(I$18&gt;0,I58*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K58" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K58" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L58" s="34"/>
       <c r="M58" s="34"/>
       <c r="N58" s="34"/>
       <c r="O58" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P58" s="9"/>
@@ -4098,18 +4196,18 @@
       <c r="H59" s="31"/>
       <c r="I59" s="31"/>
       <c r="J59" s="32" t="str">
+        <f>IFERROR(IF(OR(E59&gt;$E$18,F59&gt;$F$18,G59&gt;$G$18,H59&gt;$H$18,I59&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D59=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E59:G59)*K$17/SUM(E$18:G$18))+(H59*K$17/H$18)+(I59*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E59:G59)*K$17/SUM(E$18:G$18))+(H59*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E59:G59)*K$17/SUM(E$18:G$18))+(I59*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H59*K$17/H$18)+(I59*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E59:G59)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H59*K$17/H$18,IF(I$18&gt;0,I59*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K59" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K59" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L59" s="34"/>
       <c r="M59" s="34"/>
       <c r="N59" s="34"/>
       <c r="O59" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P59" s="9"/>
@@ -4135,18 +4233,18 @@
       <c r="H60" s="31"/>
       <c r="I60" s="31"/>
       <c r="J60" s="32" t="str">
+        <f>IFERROR(IF(OR(E60&gt;$E$18,F60&gt;$F$18,G60&gt;$G$18,H60&gt;$H$18,I60&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D60=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E60:G60)*K$17/SUM(E$18:G$18))+(H60*K$17/H$18)+(I60*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E60:G60)*K$17/SUM(E$18:G$18))+(H60*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E60:G60)*K$17/SUM(E$18:G$18))+(I60*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H60*K$17/H$18)+(I60*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E60:G60)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H60*K$17/H$18,IF(I$18&gt;0,I60*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K60" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K60" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L60" s="34"/>
       <c r="M60" s="34"/>
       <c r="N60" s="34"/>
       <c r="O60" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P60" s="9"/>
@@ -4172,18 +4270,18 @@
       <c r="H61" s="37"/>
       <c r="I61" s="37"/>
       <c r="J61" s="32" t="str">
+        <f>IFERROR(IF(OR(E61&gt;$E$18,F61&gt;$F$18,G61&gt;$G$18,H61&gt;$H$18,I61&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D61=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E61:G61)*K$17/SUM(E$18:G$18))+(H61*K$17/H$18)+(I61*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E61:G61)*K$17/SUM(E$18:G$18))+(H61*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E61:G61)*K$17/SUM(E$18:G$18))+(I61*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H61*K$17/H$18)+(I61*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E61:G61)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H61*K$17/H$18,IF(I$18&gt;0,I61*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K61" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K61" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L61" s="34"/>
       <c r="M61" s="34"/>
       <c r="N61" s="34"/>
       <c r="O61" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P61" s="9"/>
@@ -4209,11 +4307,11 @@
       <c r="H62" s="37"/>
       <c r="I62" s="37"/>
       <c r="J62" s="32" t="str">
+        <f>IFERROR(IF(OR(E62&gt;$E$18,F62&gt;$F$18,G62&gt;$G$18,H62&gt;$H$18,I62&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D62=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E62:G62)*K$17/SUM(E$18:G$18))+(H62*K$17/H$18)+(I62*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E62:G62)*K$17/SUM(E$18:G$18))+(H62*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E62:G62)*K$17/SUM(E$18:G$18))+(I62*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H62*K$17/H$18)+(I62*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E62:G62)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H62*K$17/H$18,IF(I$18&gt;0,I62*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K62" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K62" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L62" s="34">
@@ -4222,7 +4320,7 @@
       <c r="M62" s="34"/>
       <c r="N62" s="34"/>
       <c r="O62" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P62" s="9"/>
@@ -4248,18 +4346,18 @@
       <c r="H63" s="39"/>
       <c r="I63" s="39"/>
       <c r="J63" s="10" t="str">
+        <f>IFERROR(IF(OR(E63&gt;$E$18,F63&gt;$F$18,G63&gt;$G$18,H63&gt;$H$18,I63&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D63=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E63:G63)*K$17/SUM(E$18:G$18))+(H63*K$17/H$18)+(I63*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E63:G63)*K$17/SUM(E$18:G$18))+(H63*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E63:G63)*K$17/SUM(E$18:G$18))+(I63*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H63*K$17/H$18)+(I63*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E63:G63)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H63*K$17/H$18,IF(I$18&gt;0,I63*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K63" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K63" s="11" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L63" s="39"/>
       <c r="M63" s="39"/>
       <c r="N63" s="39"/>
       <c r="O63" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P63" s="9"/>
@@ -4285,11 +4383,11 @@
       <c r="H64" s="34"/>
       <c r="I64" s="34"/>
       <c r="J64" s="32" t="str">
+        <f>IFERROR(IF(OR(E64&gt;$E$18,F64&gt;$F$18,G64&gt;$G$18,H64&gt;$H$18,I64&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D64=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E64:G64)*K$17/SUM(E$18:G$18))+(H64*K$17/H$18)+(I64*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E64:G64)*K$17/SUM(E$18:G$18))+(H64*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E64:G64)*K$17/SUM(E$18:G$18))+(I64*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H64*K$17/H$18)+(I64*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E64:G64)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H64*K$17/H$18,IF(I$18&gt;0,I64*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K64" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K64" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L64" s="34">
@@ -4298,7 +4396,7 @@
       <c r="M64" s="34"/>
       <c r="N64" s="34"/>
       <c r="O64" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P64" s="9"/>
@@ -4324,11 +4422,11 @@
       <c r="H65" s="31"/>
       <c r="I65" s="31"/>
       <c r="J65" s="32" t="str">
+        <f>IFERROR(IF(OR(E65&gt;$E$18,F65&gt;$F$18,G65&gt;$G$18,H65&gt;$H$18,I65&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D65=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E65:G65)*K$17/SUM(E$18:G$18))+(H65*K$17/H$18)+(I65*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E65:G65)*K$17/SUM(E$18:G$18))+(H65*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E65:G65)*K$17/SUM(E$18:G$18))+(I65*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H65*K$17/H$18)+(I65*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E65:G65)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H65*K$17/H$18,IF(I$18&gt;0,I65*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K65" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K65" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L65" s="34">
@@ -4337,7 +4435,7 @@
       <c r="M65" s="34"/>
       <c r="N65" s="34"/>
       <c r="O65" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P65" s="9"/>
@@ -4363,18 +4461,18 @@
       <c r="H66" s="31"/>
       <c r="I66" s="31"/>
       <c r="J66" s="32" t="str">
+        <f>IFERROR(IF(OR(E66&gt;$E$18,F66&gt;$F$18,G66&gt;$G$18,H66&gt;$H$18,I66&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D66=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E66:G66)*K$17/SUM(E$18:G$18))+(H66*K$17/H$18)+(I66*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E66:G66)*K$17/SUM(E$18:G$18))+(H66*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E66:G66)*K$17/SUM(E$18:G$18))+(I66*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H66*K$17/H$18)+(I66*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E66:G66)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H66*K$17/H$18,IF(I$18&gt;0,I66*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K66" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K66" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L66" s="34"/>
       <c r="M66" s="34"/>
       <c r="N66" s="34"/>
       <c r="O66" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P66" s="9"/>
@@ -4421,11 +4519,11 @@
       <c r="H67" s="37"/>
       <c r="I67" s="37"/>
       <c r="J67" s="32" t="str">
+        <f>IFERROR(IF(OR(E67&gt;$E$18,F67&gt;$F$18,G67&gt;$G$18,H67&gt;$H$18,I67&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D67=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E67:G67)*K$17/SUM(E$18:G$18))+(H67*K$17/H$18)+(I67*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E67:G67)*K$17/SUM(E$18:G$18))+(H67*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E67:G67)*K$17/SUM(E$18:G$18))+(I67*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H67*K$17/H$18)+(I67*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E67:G67)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H67*K$17/H$18,IF(I$18&gt;0,I67*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K67" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K67" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L67" s="34">
@@ -4434,7 +4532,7 @@
       <c r="M67" s="34"/>
       <c r="N67" s="34"/>
       <c r="O67" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P67" s="9"/>
@@ -4484,18 +4582,18 @@
       <c r="H68" s="31"/>
       <c r="I68" s="31"/>
       <c r="J68" s="32" t="str">
+        <f>IFERROR(IF(OR(E68&gt;$E$18,F68&gt;$F$18,G68&gt;$G$18,H68&gt;$H$18,I68&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D68=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E68:G68)*K$17/SUM(E$18:G$18))+(H68*K$17/H$18)+(I68*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E68:G68)*K$17/SUM(E$18:G$18))+(H68*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E68:G68)*K$17/SUM(E$18:G$18))+(I68*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H68*K$17/H$18)+(I68*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E68:G68)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H68*K$17/H$18,IF(I$18&gt;0,I68*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K68" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K68" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L68" s="34"/>
       <c r="M68" s="34"/>
       <c r="N68" s="34"/>
       <c r="O68" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P68" s="9"/>
@@ -4521,11 +4619,11 @@
       <c r="H69" s="37"/>
       <c r="I69" s="37"/>
       <c r="J69" s="32" t="str">
+        <f>IFERROR(IF(OR(E69&gt;$E$18,F69&gt;$F$18,G69&gt;$G$18,H69&gt;$H$18,I69&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D69=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E69:G69)*K$17/SUM(E$18:G$18))+(H69*K$17/H$18)+(I69*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E69:G69)*K$17/SUM(E$18:G$18))+(H69*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E69:G69)*K$17/SUM(E$18:G$18))+(I69*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H69*K$17/H$18)+(I69*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E69:G69)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H69*K$17/H$18,IF(I$18&gt;0,I69*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K69" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K69" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L69" s="34">
@@ -4534,7 +4632,7 @@
       <c r="M69" s="34"/>
       <c r="N69" s="34"/>
       <c r="O69" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P69" s="9"/>
@@ -4560,18 +4658,18 @@
       <c r="H70" s="37"/>
       <c r="I70" s="37"/>
       <c r="J70" s="32" t="str">
+        <f>IFERROR(IF(OR(E70&gt;$E$18,F70&gt;$F$18,G70&gt;$G$18,H70&gt;$H$18,I70&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D70=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E70:G70)*K$17/SUM(E$18:G$18))+(H70*K$17/H$18)+(I70*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E70:G70)*K$17/SUM(E$18:G$18))+(H70*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E70:G70)*K$17/SUM(E$18:G$18))+(I70*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H70*K$17/H$18)+(I70*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E70:G70)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H70*K$17/H$18,IF(I$18&gt;0,I70*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K70" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K70" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L70" s="34"/>
       <c r="M70" s="34"/>
       <c r="N70" s="34"/>
       <c r="O70" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P70" s="9"/>
@@ -4597,11 +4695,11 @@
       <c r="H71" s="39"/>
       <c r="I71" s="39"/>
       <c r="J71" s="10" t="str">
+        <f>IFERROR(IF(OR(E71&gt;$E$18,F71&gt;$F$18,G71&gt;$G$18,H71&gt;$H$18,I71&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D71=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E71:G71)*K$17/SUM(E$18:G$18))+(H71*K$17/H$18)+(I71*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E71:G71)*K$17/SUM(E$18:G$18))+(H71*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E71:G71)*K$17/SUM(E$18:G$18))+(I71*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H71*K$17/H$18)+(I71*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E71:G71)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H71*K$17/H$18,IF(I$18&gt;0,I71*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K71" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K71" s="11" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L71" s="39">
@@ -4610,7 +4708,7 @@
       <c r="M71" s="39"/>
       <c r="N71" s="39"/>
       <c r="O71" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P71" s="9"/>
@@ -4636,18 +4734,18 @@
       <c r="H72" s="39"/>
       <c r="I72" s="39"/>
       <c r="J72" s="10" t="str">
+        <f>IFERROR(IF(OR(E72&gt;$E$18,F72&gt;$F$18,G72&gt;$G$18,H72&gt;$H$18,I72&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D72=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E72:G72)*K$17/SUM(E$18:G$18))+(H72*K$17/H$18)+(I72*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E72:G72)*K$17/SUM(E$18:G$18))+(H72*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E72:G72)*K$17/SUM(E$18:G$18))+(I72*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H72*K$17/H$18)+(I72*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E72:G72)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H72*K$17/H$18,IF(I$18&gt;0,I72*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K72" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K72" s="11" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L72" s="39"/>
       <c r="M72" s="39"/>
       <c r="N72" s="39"/>
       <c r="O72" s="11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P72" s="9"/>
@@ -4673,11 +4771,11 @@
       <c r="H73" s="34"/>
       <c r="I73" s="34"/>
       <c r="J73" s="32" t="str">
+        <f>IFERROR(IF(OR(E73&gt;$E$18,F73&gt;$F$18,G73&gt;$G$18,H73&gt;$H$18,I73&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D73=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E73:G73)*K$17/SUM(E$18:G$18))+(H73*K$17/H$18)+(I73*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E73:G73)*K$17/SUM(E$18:G$18))+(H73*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E73:G73)*K$17/SUM(E$18:G$18))+(I73*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H73*K$17/H$18)+(I73*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E73:G73)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H73*K$17/H$18,IF(I$18&gt;0,I73*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K73" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K73" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L73" s="34">
@@ -4686,7 +4784,7 @@
       <c r="M73" s="34"/>
       <c r="N73" s="34"/>
       <c r="O73" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P73" s="9"/>
@@ -4712,18 +4810,18 @@
       <c r="H74" s="31"/>
       <c r="I74" s="31"/>
       <c r="J74" s="32" t="str">
+        <f>IFERROR(IF(OR(E74&gt;$E$18,F74&gt;$F$18,G74&gt;$G$18,H74&gt;$H$18,I74&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D74=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E74:G74)*K$17/SUM(E$18:G$18))+(H74*K$17/H$18)+(I74*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E74:G74)*K$17/SUM(E$18:G$18))+(H74*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E74:G74)*K$17/SUM(E$18:G$18))+(I74*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H74*K$17/H$18)+(I74*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E74:G74)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H74*K$17/H$18,IF(I$18&gt;0,I74*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K74" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K74" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L74" s="34"/>
       <c r="M74" s="34"/>
       <c r="N74" s="34"/>
       <c r="O74" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P74" s="9"/>
@@ -4749,11 +4847,11 @@
       <c r="H75" s="37"/>
       <c r="I75" s="37"/>
       <c r="J75" s="32" t="str">
+        <f>IFERROR(IF(OR(E75&gt;$E$18,F75&gt;$F$18,G75&gt;$G$18,H75&gt;$H$18,I75&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D75=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E75:G75)*K$17/SUM(E$18:G$18))+(H75*K$17/H$18)+(I75*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E75:G75)*K$17/SUM(E$18:G$18))+(H75*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E75:G75)*K$17/SUM(E$18:G$18))+(I75*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H75*K$17/H$18)+(I75*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E75:G75)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H75*K$17/H$18,IF(I$18&gt;0,I75*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K75" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K75" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L75" s="34">
@@ -4762,7 +4860,7 @@
       <c r="M75" s="34"/>
       <c r="N75" s="34"/>
       <c r="O75" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P75" s="9"/>
@@ -4788,11 +4886,11 @@
       <c r="H76" s="37"/>
       <c r="I76" s="37"/>
       <c r="J76" s="32" t="str">
+        <f>IFERROR(IF(OR(E76&gt;$E$18,F76&gt;$F$18,G76&gt;$G$18,H76&gt;$H$18,I76&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D76=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E76:G76)*K$17/SUM(E$18:G$18))+(H76*K$17/H$18)+(I76*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E76:G76)*K$17/SUM(E$18:G$18))+(H76*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E76:G76)*K$17/SUM(E$18:G$18))+(I76*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H76*K$17/H$18)+(I76*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E76:G76)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H76*K$17/H$18,IF(I$18&gt;0,I76*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K76" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K76" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L76" s="34">
@@ -4801,7 +4899,7 @@
       <c r="M76" s="34"/>
       <c r="N76" s="34"/>
       <c r="O76" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P76" s="9"/>
@@ -4827,11 +4925,11 @@
       <c r="H77" s="37"/>
       <c r="I77" s="37"/>
       <c r="J77" s="32" t="str">
+        <f>IFERROR(IF(OR(E77&gt;$E$18,F77&gt;$F$18,G77&gt;$G$18,H77&gt;$H$18,I77&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D77=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E77:G77)*K$17/SUM(E$18:G$18))+(H77*K$17/H$18)+(I77*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E77:G77)*K$17/SUM(E$18:G$18))+(H77*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E77:G77)*K$17/SUM(E$18:G$18))+(I77*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H77*K$17/H$18)+(I77*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E77:G77)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H77*K$17/H$18,IF(I$18&gt;0,I77*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K77" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K77" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L77" s="34">
@@ -4840,7 +4938,7 @@
       <c r="M77" s="34"/>
       <c r="N77" s="34"/>
       <c r="O77" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P77" s="9"/>
@@ -4866,18 +4964,18 @@
       <c r="H78" s="31"/>
       <c r="I78" s="31"/>
       <c r="J78" s="32" t="str">
+        <f>IFERROR(IF(OR(E78&gt;$E$18,F78&gt;$F$18,G78&gt;$G$18,H78&gt;$H$18,I78&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D78=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E78:G78)*K$17/SUM(E$18:G$18))+(H78*K$17/H$18)+(I78*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E78:G78)*K$17/SUM(E$18:G$18))+(H78*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E78:G78)*K$17/SUM(E$18:G$18))+(I78*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H78*K$17/H$18)+(I78*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E78:G78)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H78*K$17/H$18,IF(I$18&gt;0,I78*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K78" s="33" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K78" s="33" t="str">
-        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="L78" s="34"/>
       <c r="M78" s="34"/>
       <c r="N78" s="34"/>
       <c r="O78" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="P78" s="9"/>
@@ -4903,11 +5001,11 @@
       <c r="H79" s="31"/>
       <c r="I79" s="31"/>
       <c r="J79" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f>IFERROR(IF(OR(E79&gt;$E$18,F79&gt;$F$18,G79&gt;$G$18,H79&gt;$H$18,I79&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D79=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E79:G79)*K$17/SUM(E$18:G$18))+(H79*K$17/H$18)+(I79*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E79:G79)*K$17/SUM(E$18:G$18))+(H79*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E79:G79)*K$17/SUM(E$18:G$18))+(I79*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H79*K$17/H$18)+(I79*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E79:G79)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H79*K$17/H$18,IF(I$18&gt;0,I79*K$17/I$18,"-")))))))))),"-")</f>
         <v/>
       </c>
       <c r="K79" s="33" t="str">
-        <f t="shared" si="1"/>
+        <f>IF($O$15="","",IF(ISTEXT(J79),"",IF(J79&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
         <v/>
       </c>
       <c r="L79" s="34">
@@ -4916,7 +5014,7 @@
       <c r="M79" s="34"/>
       <c r="N79" s="34"/>
       <c r="O79" s="33" t="str">
-        <f t="shared" si="2"/>
+        <f>IFERROR(IF(AND(ISNUMBER(J79),J79&gt;=$K$17*$P$15)," ",IF(AND(J79&gt;0,$O$16&lt;&gt;"Not yet Taught",$D79&lt;&gt;"",J79="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D79&lt;&gt;"",$L$18&gt;0,L79&gt;0,L79&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D79&lt;&gt;"",M79&gt;0,M79&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D79&lt;&gt;"",N79&gt;0,N79&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D79&lt;&gt;"",L79&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D79&lt;&gt;"",L79&lt;=0,M79&lt;=0,N79&lt;=0),"Re-Assessment",IF(AND(J79&gt;0,$D79&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
         <v/>
       </c>
       <c r="P79" s="9"/>
@@ -4927,20 +5025,37 @@
     </row>
     <row r="80" spans="1:36" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9"/>
-      <c r="B80" s="35"/>
-      <c r="C80" s="29"/>
-      <c r="D80" s="36"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="33"/>
-      <c r="L80" s="34"/>
+      <c r="B80" s="35">
+        <v>62</v>
+      </c>
+      <c r="C80" s="29">
+        <v>3</v>
+      </c>
+      <c r="D80" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31"/>
+      <c r="G80" s="31"/>
+      <c r="H80" s="31"/>
+      <c r="I80" s="31"/>
+      <c r="J80" s="32" t="str">
+        <f>IFERROR(IF(OR(E80&gt;$E$18,F80&gt;$F$18,G80&gt;$G$18,H80&gt;$H$18,I80&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D80=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E80:G80)*K$17/SUM(E$18:G$18))+(H80*K$17/H$18)+(I80*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E80:G80)*K$17/SUM(E$18:G$18))+(H80*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E80:G80)*K$17/SUM(E$18:G$18))+(I80*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H80*K$17/H$18)+(I80*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E80:G80)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H80*K$17/H$18,IF(I$18&gt;0,I80*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K80" s="33" t="str">
+        <f>IF($O$15="","",IF(ISTEXT(J80),"",IF(J80&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
+        <v/>
+      </c>
+      <c r="L80" s="34">
+        <v>11</v>
+      </c>
       <c r="M80" s="34"/>
       <c r="N80" s="34"/>
-      <c r="O80" s="33"/>
+      <c r="O80" s="33" t="str">
+        <f>IFERROR(IF(AND(ISNUMBER(J80),J80&gt;=$K$17*$P$15)," ",IF(AND(J80&gt;0,$O$16&lt;&gt;"Not yet Taught",$D80&lt;&gt;"",J80="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D80&lt;&gt;"",$L$18&gt;0,L80&gt;0,L80&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D80&lt;&gt;"",M80&gt;0,M80&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D80&lt;&gt;"",N80&gt;0,N80&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D80&lt;&gt;"",L80&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D80&lt;&gt;"",L80&lt;=0,M80&lt;=0,N80&lt;=0),"Re-Assessment",IF(AND(J80&gt;0,$D80&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
+        <v/>
+      </c>
       <c r="P80" s="9"/>
       <c r="Q80" s="9"/>
       <c r="R80" s="9"/>
@@ -4949,20 +5064,37 @@
     </row>
     <row r="81" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="9"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="34"/>
-      <c r="F81" s="34"/>
-      <c r="G81" s="34"/>
-      <c r="H81" s="34"/>
-      <c r="I81" s="34"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="33"/>
-      <c r="L81" s="34"/>
+      <c r="B81" s="35">
+        <v>61</v>
+      </c>
+      <c r="C81" s="29">
+        <v>3</v>
+      </c>
+      <c r="D81" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="31"/>
+      <c r="I81" s="31"/>
+      <c r="J81" s="32" t="str">
+        <f>IFERROR(IF(OR(E81&gt;$E$18,F81&gt;$F$18,G81&gt;$G$18,H81&gt;$H$18,I81&gt;$I$18),"-",IF(OR($H$15="",$O$16="",$K$17="",$O$15=""),"",IF(OR(SUM(E$18:I$110)&lt;=0,$D81=""),"",IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0,I$18&gt;0),((SUM(E81:G81)*K$17/SUM(E$18:G$18))+(H81*K$17/H$18)+(I81*K$17/I$18))/3,IF(AND(SUM(E$18:G$18)&gt;0,H$18&gt;0),((SUM(E81:G81)*K$17/SUM(E$18:G$18))+(H81*K$17/H$18))/2,IF(AND(SUM(E$18:G$18)&gt;0,I$18&gt;0),((SUM(E81:G81)*K$17/SUM(E$18:G$18))+(I81*K$17/I$18))/2,IF(AND(H$18&gt;0,I$18&gt;0),((H81*K$17/H$18)+(I81*K$17/I$18))/2,IF(SUM(E$18:G$18)&gt;0,SUM(E81:G81)*K$17/SUM(E$18:G$18),IF(H$18&gt;0,H81*K$17/H$18,IF(I$18&gt;0,I81*K$17/I$18,"-")))))))))),"-")</f>
+        <v/>
+      </c>
+      <c r="K81" s="33" t="str">
+        <f>IF($O$15="","",IF(ISTEXT(J81),"",IF(J81&gt;=$K$17*$P$15,"Competent","Not yet Competent")))</f>
+        <v/>
+      </c>
+      <c r="L81" s="34">
+        <v>16</v>
+      </c>
       <c r="M81" s="34"/>
       <c r="N81" s="34"/>
-      <c r="O81" s="33"/>
+      <c r="O81" s="33" t="str">
+        <f>IFERROR(IF(AND(ISNUMBER(J81),J81&gt;=$K$17*$P$15)," ",IF(AND(J81&gt;0,$O$16&lt;&gt;"Not yet Taught",$D81&lt;&gt;"",J81="-"),"Not yet Assessed",IF(AND($O$16="Completed",$D81&lt;&gt;"",$L$18&gt;0,L81&gt;0,L81&gt;=$L$18*$P$15),"Competent",IF(AND($O$16="Completed",$M$18&gt;0,$D81&lt;&gt;"",M81&gt;0,M81&gt;=$M$18*$P$15),"Competent",IF(AND($O$16="Completed",$N$18&gt;0,$D81&lt;&gt;"",N81&gt;0,N81&gt;=$N$18*$P$15),"Competent",IF(AND($O$16="Completed",$D81&lt;&gt;"",L81&lt;$N$18*$P$15),"Re-Assessment",IF(AND($O$16="Completed",SUM($N$18:$N$18)&lt;=0,$D81&lt;&gt;"",L81&lt;=0,M81&lt;=0,N81&lt;=0),"Re-Assessment",IF(AND(J81&gt;0,$D81&lt;&gt;"",$O$16="Ongoing"),"Ongoing","")))))))),"")</f>
+        <v/>
+      </c>
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -4973,12 +5105,12 @@
       <c r="A82" s="9"/>
       <c r="B82" s="35"/>
       <c r="C82" s="29"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="34"/>
-      <c r="I82" s="34"/>
+      <c r="D82" s="36"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
       <c r="J82" s="32"/>
       <c r="K82" s="33"/>
       <c r="L82" s="34"/>
@@ -4995,12 +5127,12 @@
       <c r="A83" s="9"/>
       <c r="B83" s="28"/>
       <c r="C83" s="29"/>
-      <c r="D83" s="36"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
       <c r="J83" s="32"/>
       <c r="K83" s="33"/>
       <c r="L83" s="34"/>
@@ -5017,7 +5149,7 @@
       <c r="A84" s="9"/>
       <c r="B84" s="35"/>
       <c r="C84" s="29"/>
-      <c r="D84" s="38"/>
+      <c r="D84" s="30"/>
       <c r="E84" s="34"/>
       <c r="F84" s="34"/>
       <c r="G84" s="34"/>
@@ -5037,7 +5169,7 @@
     </row>
     <row r="85" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9"/>
-      <c r="B85" s="35"/>
+      <c r="B85" s="28"/>
       <c r="C85" s="29"/>
       <c r="D85" s="36"/>
       <c r="E85" s="37"/>
@@ -5059,14 +5191,14 @@
     </row>
     <row r="86" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9"/>
-      <c r="B86" s="28"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="29"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="37"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="34"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="34"/>
+      <c r="I86" s="34"/>
       <c r="J86" s="32"/>
       <c r="K86" s="33"/>
       <c r="L86" s="34"/>
@@ -5081,14 +5213,14 @@
     </row>
     <row r="87" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9"/>
-      <c r="B87" s="28"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="29"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="34"/>
-      <c r="F87" s="34"/>
-      <c r="G87" s="34"/>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="37"/>
+      <c r="F87" s="37"/>
+      <c r="G87" s="37"/>
+      <c r="H87" s="37"/>
+      <c r="I87" s="37"/>
       <c r="J87" s="32"/>
       <c r="K87" s="33"/>
       <c r="L87" s="34"/>
@@ -5103,7 +5235,7 @@
     </row>
     <row r="88" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9"/>
-      <c r="B88" s="35"/>
+      <c r="B88" s="28"/>
       <c r="C88" s="29"/>
       <c r="D88" s="36"/>
       <c r="E88" s="37"/>
@@ -5127,12 +5259,12 @@
       <c r="A89" s="9"/>
       <c r="B89" s="28"/>
       <c r="C89" s="29"/>
-      <c r="D89" s="36"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="37"/>
-      <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="34"/>
+      <c r="F89" s="34"/>
+      <c r="G89" s="34"/>
+      <c r="H89" s="34"/>
+      <c r="I89" s="34"/>
       <c r="J89" s="32"/>
       <c r="K89" s="33"/>
       <c r="L89" s="34"/>
@@ -5147,7 +5279,7 @@
     </row>
     <row r="90" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9"/>
-      <c r="B90" s="28"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="29"/>
       <c r="D90" s="36"/>
       <c r="E90" s="37"/>
@@ -5191,14 +5323,14 @@
     </row>
     <row r="92" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9"/>
-      <c r="B92" s="35"/>
+      <c r="B92" s="28"/>
       <c r="C92" s="29"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="34"/>
-      <c r="F92" s="34"/>
-      <c r="G92" s="34"/>
-      <c r="H92" s="34"/>
-      <c r="I92" s="34"/>
+      <c r="D92" s="36"/>
+      <c r="E92" s="37"/>
+      <c r="F92" s="37"/>
+      <c r="G92" s="37"/>
+      <c r="H92" s="37"/>
+      <c r="I92" s="37"/>
       <c r="J92" s="32"/>
       <c r="K92" s="33"/>
       <c r="L92" s="34"/>
@@ -5215,12 +5347,12 @@
       <c r="A93" s="9"/>
       <c r="B93" s="28"/>
       <c r="C93" s="29"/>
-      <c r="D93" s="30"/>
-      <c r="E93" s="34"/>
-      <c r="F93" s="34"/>
-      <c r="G93" s="34"/>
-      <c r="H93" s="34"/>
-      <c r="I93" s="34"/>
+      <c r="D93" s="36"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="37"/>
+      <c r="H93" s="37"/>
+      <c r="I93" s="37"/>
       <c r="J93" s="32"/>
       <c r="K93" s="33"/>
       <c r="L93" s="34"/>
@@ -5257,14 +5389,14 @@
     </row>
     <row r="95" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9"/>
-      <c r="B95" s="35"/>
+      <c r="B95" s="28"/>
       <c r="C95" s="29"/>
       <c r="D95" s="30"/>
-      <c r="E95" s="31"/>
-      <c r="F95" s="31"/>
-      <c r="G95" s="31"/>
-      <c r="H95" s="31"/>
-      <c r="I95" s="31"/>
+      <c r="E95" s="34"/>
+      <c r="F95" s="34"/>
+      <c r="G95" s="34"/>
+      <c r="H95" s="34"/>
+      <c r="I95" s="34"/>
       <c r="J95" s="32"/>
       <c r="K95" s="33"/>
       <c r="L95" s="34"/>
@@ -5301,14 +5433,14 @@
     </row>
     <row r="97" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="9"/>
-      <c r="B97" s="28"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="29"/>
-      <c r="D97" s="36"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="37"/>
-      <c r="H97" s="37"/>
-      <c r="I97" s="37"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="31"/>
+      <c r="F97" s="31"/>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31"/>
+      <c r="I97" s="31"/>
       <c r="J97" s="32"/>
       <c r="K97" s="33"/>
       <c r="L97" s="34"/>
@@ -5325,12 +5457,12 @@
       <c r="A98" s="9"/>
       <c r="B98" s="35"/>
       <c r="C98" s="29"/>
-      <c r="D98" s="36"/>
-      <c r="E98" s="39"/>
-      <c r="F98" s="39"/>
-      <c r="G98" s="39"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+      <c r="G98" s="34"/>
+      <c r="H98" s="34"/>
+      <c r="I98" s="34"/>
       <c r="J98" s="32"/>
       <c r="K98" s="33"/>
       <c r="L98" s="34"/>
@@ -5348,11 +5480,11 @@
       <c r="B99" s="28"/>
       <c r="C99" s="29"/>
       <c r="D99" s="36"/>
-      <c r="E99" s="39"/>
-      <c r="F99" s="39"/>
-      <c r="G99" s="39"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
+      <c r="E99" s="37"/>
+      <c r="F99" s="37"/>
+      <c r="G99" s="37"/>
+      <c r="H99" s="37"/>
+      <c r="I99" s="37"/>
       <c r="J99" s="32"/>
       <c r="K99" s="33"/>
       <c r="L99" s="34"/>
@@ -5433,6 +5565,20 @@
     </row>
     <row r="103" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9"/>
+      <c r="B103" s="28"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="39"/>
+      <c r="F103" s="39"/>
+      <c r="G103" s="39"/>
+      <c r="H103" s="39"/>
+      <c r="I103" s="39"/>
+      <c r="J103" s="32"/>
+      <c r="K103" s="33"/>
+      <c r="L103" s="34"/>
+      <c r="M103" s="34"/>
+      <c r="N103" s="34"/>
+      <c r="O103" s="33"/>
       <c r="P103" s="9"/>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -5441,7 +5587,7 @@
     </row>
     <row r="104" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9"/>
-      <c r="B104" s="28"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="29"/>
       <c r="D104" s="36"/>
       <c r="E104" s="39"/>
@@ -5463,20 +5609,6 @@
     </row>
     <row r="105" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9"/>
-      <c r="B105" s="35"/>
-      <c r="C105" s="29"/>
-      <c r="D105" s="36"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="39"/>
-      <c r="I105" s="39"/>
-      <c r="J105" s="32"/>
-      <c r="K105" s="33"/>
-      <c r="L105" s="34"/>
-      <c r="M105" s="34"/>
-      <c r="N105" s="34"/>
-      <c r="O105" s="33"/>
       <c r="P105" s="9"/>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -5619,6 +5751,7 @@
       <c r="A112" s="9"/>
       <c r="B112" s="28"/>
       <c r="C112" s="29"/>
+      <c r="D112" s="36"/>
       <c r="E112" s="39"/>
       <c r="F112" s="39"/>
       <c r="G112" s="39"/>
@@ -5638,8 +5771,9 @@
     </row>
     <row r="113" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9"/>
-      <c r="B113" s="28"/>
+      <c r="B113" s="35"/>
       <c r="C113" s="29"/>
+      <c r="D113" s="36"/>
       <c r="E113" s="39"/>
       <c r="F113" s="39"/>
       <c r="G113" s="39"/>
@@ -5785,6 +5919,19 @@
     </row>
     <row r="120" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="9"/>
+      <c r="B120" s="28"/>
+      <c r="C120" s="29"/>
+      <c r="E120" s="39"/>
+      <c r="F120" s="39"/>
+      <c r="G120" s="39"/>
+      <c r="H120" s="39"/>
+      <c r="I120" s="39"/>
+      <c r="J120" s="32"/>
+      <c r="K120" s="33"/>
+      <c r="L120" s="34"/>
+      <c r="M120" s="34"/>
+      <c r="N120" s="34"/>
+      <c r="O120" s="33"/>
       <c r="P120" s="9"/>
       <c r="Q120" s="9"/>
       <c r="R120" s="9"/>
@@ -5814,19 +5961,6 @@
     </row>
     <row r="122" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9"/>
-      <c r="B122" s="28"/>
-      <c r="C122" s="29"/>
-      <c r="E122" s="39"/>
-      <c r="F122" s="39"/>
-      <c r="G122" s="39"/>
-      <c r="H122" s="39"/>
-      <c r="I122" s="39"/>
-      <c r="J122" s="32"/>
-      <c r="K122" s="33"/>
-      <c r="L122" s="34"/>
-      <c r="M122" s="34"/>
-      <c r="N122" s="34"/>
-      <c r="O122" s="33"/>
       <c r="P122" s="9"/>
       <c r="Q122" s="9"/>
       <c r="R122" s="9"/>
@@ -5863,9 +5997,12 @@
       <c r="G124" s="39"/>
       <c r="H124" s="39"/>
       <c r="I124" s="39"/>
-      <c r="L124" s="39"/>
-      <c r="M124" s="39"/>
-      <c r="N124" s="39"/>
+      <c r="J124" s="32"/>
+      <c r="K124" s="33"/>
+      <c r="L124" s="34"/>
+      <c r="M124" s="34"/>
+      <c r="N124" s="34"/>
+      <c r="O124" s="33"/>
       <c r="P124" s="9"/>
       <c r="Q124" s="9"/>
       <c r="R124" s="9"/>
@@ -5874,15 +6011,19 @@
     </row>
     <row r="125" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="9"/>
+      <c r="B125" s="28"/>
       <c r="C125" s="29"/>
       <c r="E125" s="39"/>
       <c r="F125" s="39"/>
       <c r="G125" s="39"/>
       <c r="H125" s="39"/>
       <c r="I125" s="39"/>
-      <c r="L125" s="39"/>
-      <c r="M125" s="39"/>
-      <c r="N125" s="39"/>
+      <c r="J125" s="32"/>
+      <c r="K125" s="33"/>
+      <c r="L125" s="34"/>
+      <c r="M125" s="34"/>
+      <c r="N125" s="34"/>
+      <c r="O125" s="33"/>
       <c r="P125" s="9"/>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -5890,6 +6031,9 @@
       <c r="T125" s="9"/>
     </row>
     <row r="126" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="9"/>
+      <c r="B126" s="28"/>
+      <c r="C126" s="29"/>
       <c r="E126" s="39"/>
       <c r="F126" s="39"/>
       <c r="G126" s="39"/>
@@ -5898,25 +6042,30 @@
       <c r="L126" s="39"/>
       <c r="M126" s="39"/>
       <c r="N126" s="39"/>
+      <c r="P126" s="9"/>
+      <c r="Q126" s="9"/>
+      <c r="R126" s="9"/>
+      <c r="S126" s="9"/>
+      <c r="T126" s="9"/>
     </row>
     <row r="127" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="35"/>
+      <c r="A127" s="9"/>
       <c r="C127" s="29"/>
-      <c r="D127" s="36"/>
-      <c r="E127" s="37"/>
-      <c r="F127" s="37"/>
-      <c r="G127" s="37"/>
-      <c r="H127" s="37"/>
-      <c r="I127" s="37"/>
-      <c r="J127" s="32"/>
-      <c r="K127" s="33"/>
-      <c r="L127" s="34"/>
-      <c r="M127" s="34"/>
-      <c r="N127" s="34"/>
-      <c r="O127" s="33"/>
+      <c r="E127" s="39"/>
+      <c r="F127" s="39"/>
+      <c r="G127" s="39"/>
+      <c r="H127" s="39"/>
+      <c r="I127" s="39"/>
+      <c r="L127" s="39"/>
+      <c r="M127" s="39"/>
+      <c r="N127" s="39"/>
+      <c r="P127" s="9"/>
+      <c r="Q127" s="9"/>
+      <c r="R127" s="9"/>
+      <c r="S127" s="9"/>
+      <c r="T127" s="9"/>
     </row>
     <row r="128" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C128" s="29"/>
       <c r="E128" s="39"/>
       <c r="F128" s="39"/>
       <c r="G128" s="39"/>
@@ -5927,30 +6076,31 @@
       <c r="N128" s="39"/>
     </row>
     <row r="129" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E129" s="39"/>
-      <c r="F129" s="39"/>
-      <c r="G129" s="39"/>
-      <c r="H129" s="39"/>
-      <c r="I129" s="39"/>
-      <c r="L129" s="39"/>
-      <c r="M129" s="39"/>
-      <c r="N129" s="39"/>
+      <c r="B129" s="35"/>
+      <c r="C129" s="29"/>
+      <c r="D129" s="36"/>
+      <c r="E129" s="37"/>
+      <c r="F129" s="37"/>
+      <c r="G129" s="37"/>
+      <c r="H129" s="37"/>
+      <c r="I129" s="37"/>
+      <c r="J129" s="32"/>
+      <c r="K129" s="33"/>
+      <c r="L129" s="34"/>
+      <c r="M129" s="34"/>
+      <c r="N129" s="34"/>
+      <c r="O129" s="33"/>
     </row>
     <row r="130" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="35"/>
       <c r="C130" s="29"/>
-      <c r="D130" s="36"/>
-      <c r="E130" s="37"/>
-      <c r="F130" s="37"/>
-      <c r="G130" s="37"/>
-      <c r="H130" s="37"/>
-      <c r="I130" s="37"/>
-      <c r="J130" s="32"/>
-      <c r="K130" s="33"/>
-      <c r="L130" s="34"/>
-      <c r="M130" s="34"/>
-      <c r="N130" s="34"/>
-      <c r="O130" s="33"/>
+      <c r="E130" s="39"/>
+      <c r="F130" s="39"/>
+      <c r="G130" s="39"/>
+      <c r="H130" s="39"/>
+      <c r="I130" s="39"/>
+      <c r="L130" s="39"/>
+      <c r="M130" s="39"/>
+      <c r="N130" s="39"/>
     </row>
     <row r="131" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E131" s="39"/>
@@ -5963,46 +6113,70 @@
       <c r="N131" s="39"/>
     </row>
     <row r="132" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E132" s="39"/>
-      <c r="F132" s="39"/>
-      <c r="G132" s="39"/>
-      <c r="H132" s="39"/>
-      <c r="I132" s="39"/>
-      <c r="L132" s="39"/>
-      <c r="M132" s="39"/>
-      <c r="N132" s="39"/>
+      <c r="B132" s="35"/>
+      <c r="C132" s="29"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="37"/>
+      <c r="F132" s="37"/>
+      <c r="G132" s="37"/>
+      <c r="H132" s="37"/>
+      <c r="I132" s="37"/>
+      <c r="J132" s="32"/>
+      <c r="K132" s="33"/>
+      <c r="L132" s="34"/>
+      <c r="M132" s="34"/>
+      <c r="N132" s="34"/>
+      <c r="O132" s="33"/>
     </row>
     <row r="133" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
       <c r="E133" s="39"/>
       <c r="F133" s="39"/>
       <c r="G133" s="39"/>
       <c r="H133" s="39"/>
       <c r="I133" s="39"/>
-      <c r="J133" s="39"/>
       <c r="L133" s="39"/>
       <c r="M133" s="39"/>
       <c r="N133" s="39"/>
     </row>
     <row r="134" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
+      <c r="E134" s="39"/>
+      <c r="F134" s="39"/>
+      <c r="G134" s="39"/>
+      <c r="H134" s="39"/>
+      <c r="I134" s="39"/>
       <c r="L134" s="39"/>
       <c r="M134" s="39"/>
       <c r="N134" s="39"/>
-      <c r="O134" s="4"/>
     </row>
     <row r="135" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
+      <c r="E135" s="39"/>
+      <c r="F135" s="39"/>
+      <c r="G135" s="39"/>
+      <c r="H135" s="39"/>
+      <c r="I135" s="39"/>
+      <c r="J135" s="39"/>
       <c r="L135" s="39"/>
       <c r="M135" s="39"/>
       <c r="N135" s="39"/>
-      <c r="O135" s="4"/>
-    </row>
-    <row r="136" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="136" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="4"/>
+      <c r="C136" s="4"/>
+      <c r="L136" s="39"/>
+      <c r="M136" s="39"/>
+      <c r="N136" s="39"/>
+      <c r="O136" s="4"/>
+    </row>
+    <row r="137" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="4"/>
+      <c r="C137" s="4"/>
+      <c r="L137" s="39"/>
+      <c r="M137" s="39"/>
+      <c r="N137" s="39"/>
+      <c r="O137" s="4"/>
+    </row>
     <row r="138" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="139" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="140" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6015,23 +6189,23 @@
     <row r="147" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="148" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="149" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="28"/>
-      <c r="C150" s="29"/>
-      <c r="E150" s="39"/>
-      <c r="F150" s="39"/>
-      <c r="G150" s="39"/>
-      <c r="H150" s="39"/>
-      <c r="I150" s="39"/>
-      <c r="J150" s="32"/>
-      <c r="K150" s="33"/>
-      <c r="L150" s="34"/>
-      <c r="M150" s="34"/>
-      <c r="N150" s="34"/>
-      <c r="O150" s="33"/>
-    </row>
+    <row r="150" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="151" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="28"/>
+      <c r="C152" s="29"/>
+      <c r="E152" s="39"/>
+      <c r="F152" s="39"/>
+      <c r="G152" s="39"/>
+      <c r="H152" s="39"/>
+      <c r="I152" s="39"/>
+      <c r="J152" s="32"/>
+      <c r="K152" s="33"/>
+      <c r="L152" s="34"/>
+      <c r="M152" s="34"/>
+      <c r="N152" s="34"/>
+      <c r="O152" s="33"/>
+    </row>
     <row r="153" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="154" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="155" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6040,24 +6214,24 @@
     <row r="158" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="159" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="160" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="35"/>
-      <c r="C161" s="29"/>
-      <c r="D161" s="30"/>
-      <c r="E161" s="34"/>
-      <c r="F161" s="34"/>
-      <c r="G161" s="34"/>
-      <c r="H161" s="34"/>
-      <c r="I161" s="34"/>
-      <c r="J161" s="32"/>
-      <c r="K161" s="33"/>
-      <c r="L161" s="34"/>
-      <c r="M161" s="34"/>
-      <c r="N161" s="34"/>
-      <c r="O161" s="33"/>
-    </row>
+    <row r="161" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="162" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="35"/>
+      <c r="C163" s="29"/>
+      <c r="D163" s="30"/>
+      <c r="E163" s="34"/>
+      <c r="F163" s="34"/>
+      <c r="G163" s="34"/>
+      <c r="H163" s="34"/>
+      <c r="I163" s="34"/>
+      <c r="J163" s="32"/>
+      <c r="K163" s="33"/>
+      <c r="L163" s="34"/>
+      <c r="M163" s="34"/>
+      <c r="N163" s="34"/>
+      <c r="O163" s="33"/>
+    </row>
     <row r="164" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="165" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="166" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6071,8 +6245,10 @@
     <row r="174" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="175" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="176" spans="2:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WMW8/E0a90rlBQu4js20pynCB1HCo9wrpAk9wNSigbiyWGAeILZSFJdUIhG57yM6PGajDMU6GW0bWDbnev+ydA==" saltValue="qfL4VOVo4FOPiTdYHm9qKA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="D10:K10"/>
     <mergeCell ref="B11:C11"/>
@@ -6090,35 +6266,93 @@
     <mergeCell ref="E16:J16"/>
     <mergeCell ref="L16:N16"/>
   </mergeCells>
-  <conditionalFormatting sqref="G109:O120 B19:O108">
-    <cfRule type="expression" dxfId="5" priority="6">
+  <conditionalFormatting sqref="G111:O122 B82:O110 B19:O80">
+    <cfRule type="expression" dxfId="15" priority="14">
       <formula>$C19&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J19:K120 O19:O120">
-    <cfRule type="expression" dxfId="4" priority="5">
+  <conditionalFormatting sqref="O82:O122 J82:K122 O19:O80 J19:K80">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>$C19&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:T1966">
-    <cfRule type="expression" dxfId="3" priority="4">
+  <conditionalFormatting sqref="A19:T78 A80:T80 A82:T1968 B79:O80">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>$C19=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K19:K120">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Not yet Competent">
+  <conditionalFormatting sqref="K82:K122 K19:K80">
+    <cfRule type="containsText" dxfId="12" priority="11" operator="containsText" text="Not yet Competent">
       <formula>NOT(ISERROR(SEARCH("Not yet Competent",K19)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O19:O120">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Ongoing">
+  <conditionalFormatting sqref="O82:O122 O19:O80">
+    <cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Ongoing">
       <formula>NOT(ISERROR(SEARCH("Ongoing",O19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Re-Assessment">
+    <cfRule type="containsText" dxfId="10" priority="10" operator="containsText" text="Re-Assessment">
       <formula>NOT(ISERROR(SEARCH("Re-Assessment",O19)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A81 C79 P81:T81">
+    <cfRule type="expression" dxfId="9" priority="24">
+      <formula>$C77=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A79 P79:T79">
+    <cfRule type="expression" dxfId="8" priority="26">
+      <formula>#REF!=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C80">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$C78=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81:O81">
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>$C81&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O81 J81:K81">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$C81&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81:O81">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>$C81=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K81">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Not yet Competent">
+      <formula>NOT(ISERROR(SEARCH("Not yet Competent",K81)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O81">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Ongoing">
+      <formula>NOT(ISERROR(SEARCH("Ongoing",O81)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Re-Assessment">
+      <formula>NOT(ISERROR(SEARCH("Re-Assessment",O81)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C81">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>$C79=""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O15">
+      <formula1>"SM,GM,CM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="O16">
+      <formula1>"Completed,Ongoing,Not yet Taught"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11">
+      <formula1>"FIRST TERM,SECOND TERM,THIRD TERM"</formula1>
+    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:O13"/>
     <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="These Data are Allready Exist" error="Please these Records are allready exist, Try to Enter the New one" sqref="D52:D54">
       <formula1>COUNTIFS($E$7:$E$1048576,$E52,$F$7:$F$1048576,$F52)&lt;=1</formula1>
     </dataValidation>
@@ -6128,19 +6362,9 @@
     <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="These Data are Allready Exist" error="Please these Records are allready exist, Try to Enter the New one" sqref="D46">
       <formula1>COUNTIFS($D$6:$D$1048576,$D50,$E$6:$E$1048576,$E46)&lt;=1</formula1>
     </dataValidation>
-    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="These Data are Allready Exist" error="Please these Records are allready exist, Try to Enter the New one" sqref="D51 D47:D49 D19:D45 D55">
+    <dataValidation type="custom" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="These Data are Allready Exist" error="Please these Records are allready exist, Try to Enter the New one" sqref="D51 D55 D19:D45 D47:D49">
       <formula1>COUNTIFS($D$6:$D$1048576,$D19,$E$6:$E$1048576,$E19)&lt;=1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O15">
-      <formula1>"SM,GM,CM"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="O16">
-      <formula1>"Completed,Ongoing,Not yet Taught"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11">
-      <formula1>"FIRST TERM,SECOND TERM,THIRD TERM"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:N13 O13"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
